--- a/artfynd/A 2888-2024 artfynd.xlsx
+++ b/artfynd/A 2888-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2888-2024 artfynd.xlsx
+++ b/artfynd/A 2888-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>81396082</v>
       </c>
       <c r="B2" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453686.9707173184</v>
+        <v>453687</v>
       </c>
       <c r="R2" t="n">
-        <v>6224328.537371795</v>
+        <v>6224329</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -752,19 +747,9 @@
           <t>2014-08-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-08-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,12 +784,7 @@
         <v>81396413</v>
       </c>
       <c r="B3" t="n">
-        <v>101325</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104255</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453730.7969596256</v>
+        <v>453731</v>
       </c>
       <c r="R3" t="n">
-        <v>6224253.451742104</v>
+        <v>6224253</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -873,19 +853,9 @@
           <t>2014-08-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-08-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,140 +884,6 @@
           <t>Skånes Flora Millora 2008-2015</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>94957435</v>
-      </c>
-      <c r="B4" t="n">
-        <v>41765</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>100768</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Flenörtskapuschongfly</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Cucullia scrophulariae</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>dike intill kostgjord damm, Arkelstorp, Sk</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>453679.2027635964</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6224022.926421404</v>
-      </c>
-      <c r="S4" t="n">
-        <v>8</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Kristianstad</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Österslöv</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2021-07-04</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2021-07-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Ronnie Jöneros</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Ronnie Jöneros</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2888-2024 artfynd.xlsx
+++ b/artfynd/A 2888-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
           <t>Skånes Flora Millora 2008-2015</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81396082</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,8 +894,17 @@
           <t>Skånes Flora Millora 2008-2015</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81396413</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>